--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Mistral-Small-3.2-24B-Instruct-2506/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Mistral-Small-3.2-24B-Instruct-2506/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.07518796992481203</v>
+        <v>0.07407407407407407</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.09154929577464789</v>
+        <v>0.08450704225352113</v>
       </c>
       <c r="D2">
-        <v>0.9280575539568345</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="E2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
